--- a/output/pdf_financials_xlsx/NEXU.xlsx
+++ b/output/pdf_financials_xlsx/NEXU.xlsx
@@ -612,10 +612,10 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.02326</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.01025</v>
       </c>
     </row>
     <row r="13">
@@ -864,10 +864,10 @@
         <v>-1.522611</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-12.662778</v>
+        <v>-12.686038</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-13.043721</v>
+        <v>-13.053971</v>
       </c>
     </row>
     <row r="28">
@@ -896,10 +896,10 @@
         <v>-1.522611</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-12.662778</v>
+        <v>-12.686038</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-13.043721</v>
+        <v>-13.053971</v>
       </c>
     </row>
     <row r="30">
@@ -976,13 +976,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.241952</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>2.693928</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.633816</v>
       </c>
     </row>
     <row r="35">
@@ -1008,13 +1008,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1.241952</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>2.693928</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.633816</v>
       </c>
     </row>
     <row r="37">
@@ -1200,13 +1200,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1.302777</v>
+        <v>0.060825</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>2.789263</v>
+        <v>0.095335</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.376414</v>
+        <v>0.742598</v>
       </c>
     </row>
     <row r="49">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -5202,7 +5202,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">

--- a/output/pdf_financials_xlsx/NEXU.xlsx
+++ b/output/pdf_financials_xlsx/NEXU.xlsx
@@ -1474,13 +1474,13 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.089356</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.020426</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.549421</v>
       </c>
     </row>
     <row r="65">
@@ -1522,13 +1522,13 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.006364</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.07398100000000001</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.07219200000000001</v>
       </c>
     </row>
     <row r="68">
